--- a/diseases/d043/2015-2019.xlsx
+++ b/diseases/d043/2015-2019.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1753,9 +1750,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2439,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3137,9 +3128,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3829,9 +3817,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4521,9 +4506,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -5213,9 +5195,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5905,9 +5884,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6597,9 +6573,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7289,9 +7262,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7981,9 +7951,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8673,9 +8640,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9365,9 +9329,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10057,9 +10018,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10749,9 +10707,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11441,9 +11396,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12133,9 +12085,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12825,9 +12774,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13517,9 +13463,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14209,9 +14152,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14901,9 +14841,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -15593,9 +15530,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16285,9 +16219,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -16976,9 +16907,6 @@
       </c>
       <c r="O96" t="n">
         <v>1</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0.01909861051878893</v>
